--- a/Resources/Spike Timing Test Data.xlsx
+++ b/Resources/Spike Timing Test Data.xlsx
@@ -8,19 +8,32 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Aaron\Documents\Unity\Projects\unity-kings-of-the-beach\Resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:9_{CD1B6DE6-B333-4999-84A9-A07BE61E1C3F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5783589A-878F-45BD-9B0A-33C269213041}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-103" yWindow="-103" windowWidth="33120" windowHeight="18000" xr2:uid="{61D222C5-DB9B-47EE-BD55-CC64417CE47A}"/>
   </bookViews>
   <sheets>
     <sheet name="log_20260513_180849" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="103" uniqueCount="6">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="128" uniqueCount="8">
   <si>
     <t>Time</t>
   </si>
@@ -38,6 +51,12 @@
   </si>
   <si>
     <t>Mama</t>
+  </si>
+  <si>
+    <t>Zachabee</t>
+  </si>
+  <si>
+    <t>Zachary</t>
   </si>
 </sst>
 </file>
@@ -1059,7 +1078,7 @@
           <c:order val="3"/>
           <c:tx>
             <c:strRef>
-              <c:f>log_20260513_180849!$H$1</c:f>
+              <c:f>log_20260513_180849!$I$1</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
               </c:strCache>
@@ -1083,7 +1102,7 @@
           </c:marker>
           <c:val>
             <c:numRef>
-              <c:f>log_20260513_180849!$H$2:$H$34</c:f>
+              <c:f>log_20260513_180849!$I$2:$I$34</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="33"/>
@@ -1201,7 +1220,7 @@
           <c:order val="4"/>
           <c:tx>
             <c:strRef>
-              <c:f>log_20260513_180849!$I$1</c:f>
+              <c:f>log_20260513_180849!$J$1</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
               </c:strCache>
@@ -1225,7 +1244,7 @@
           </c:marker>
           <c:val>
             <c:numRef>
-              <c:f>log_20260513_180849!$I$2:$I$34</c:f>
+              <c:f>log_20260513_180849!$J$2:$J$34</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="33"/>
@@ -1343,7 +1362,7 @@
           <c:order val="5"/>
           <c:tx>
             <c:strRef>
-              <c:f>log_20260513_180849!$J$1</c:f>
+              <c:f>log_20260513_180849!$K$1</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
               </c:strCache>
@@ -1367,7 +1386,7 @@
           </c:marker>
           <c:val>
             <c:numRef>
-              <c:f>log_20260513_180849!$J$2:$J$34</c:f>
+              <c:f>log_20260513_180849!$K$2:$K$34</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="33"/>
@@ -1477,6 +1496,269 @@
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
               <c16:uniqueId val="{00000005-2807-43B9-9962-118052CD4B81}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="6"/>
+          <c:order val="6"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>log_20260513_180849!$H$1</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Zachary</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent1">
+                  <a:lumMod val="50000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="7"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent1">
+                  <a:lumMod val="60000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="bg1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:val>
+            <c:numRef>
+              <c:f>log_20260513_180849!$H$2:$H$34</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="33"/>
+                <c:pt idx="0">
+                  <c:v>0.30960470000000001</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.24119489999999999</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.42393150000000002</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0.17542440000000001</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0.19900319999999999</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>0.30479679999999998</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>0.23587359999999999</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>0.19466820000000001</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>0.31722230000000001</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>0.22456699999999999</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>0.13658439999999999</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>0.210925</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>0.22223200000000001</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>0.23358699999999999</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>0.29023840000000001</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>0.29136600000000001</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>0.1194267</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>0.26140530000000001</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>0.20653779999999999</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>0.24643580000000001</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>0.35012680000000002</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>0.24102000000000001</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>0.30813099999999999</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>0.3412654</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-E0C9-441A-8B2F-BCF6D2245460}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="7"/>
+          <c:order val="7"/>
+          <c:spPr>
+            <a:ln w="19050" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent2">
+                  <a:lumMod val="50000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:prstDash val="sysDot"/>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:val>
+            <c:numRef>
+              <c:f>log_20260513_180849!$L$2:$L$34</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="33"/>
+                <c:pt idx="0">
+                  <c:v>0.25356534166666667</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.25356534166666667</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.25356534166666667</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0.25356534166666667</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0.25356534166666667</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>0.25356534166666667</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>0.25356534166666667</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>0.25356534166666667</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>0.25356534166666667</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>0.25356534166666667</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>0.25356534166666667</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>0.25356534166666667</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>0.25356534166666667</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>0.25356534166666667</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>0.25356534166666667</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>0.25356534166666667</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>0.25356534166666667</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>0.25356534166666667</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>0.25356534166666667</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>0.25356534166666667</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>0.25356534166666667</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>0.25356534166666667</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>0.25356534166666667</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>0.25356534166666667</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>0.25356534166666667</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>0.25356534166666667</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>0.25356534166666667</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>0.25356534166666667</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>0.25356534166666667</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>0.25356534166666667</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>0.25356534166666667</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>0.25356534166666667</c:v>
+                </c:pt>
+                <c:pt idx="32">
+                  <c:v>0.25356534166666667</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000001-E0C9-441A-8B2F-BCF6D2245460}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -1586,6 +1868,10 @@
       </c:legendEntry>
       <c:legendEntry>
         <c:idx val="5"/>
+        <c:delete val="1"/>
+      </c:legendEntry>
+      <c:legendEntry>
+        <c:idx val="7"/>
         <c:delete val="1"/>
       </c:legendEntry>
       <c:overlay val="0"/>
@@ -2221,13 +2507,13 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>11</xdr:col>
+      <xdr:col>12</xdr:col>
       <xdr:colOff>323850</xdr:colOff>
       <xdr:row>4</xdr:row>
       <xdr:rowOff>84361</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>24</xdr:col>
+      <xdr:col>25</xdr:col>
       <xdr:colOff>223158</xdr:colOff>
       <xdr:row>30</xdr:row>
       <xdr:rowOff>21772</xdr:rowOff>
@@ -2555,10 +2841,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F856A869-2802-480F-83A9-508A0697CF30}">
-  <dimension ref="A1:J98"/>
+  <dimension ref="A1:L122"/>
   <sheetFormatPr defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -2577,8 +2863,11 @@
       <c r="G1" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="H1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A2">
         <v>2.5</v>
       </c>
@@ -2598,19 +2887,26 @@
         <v>0.30935010000000002</v>
       </c>
       <c r="H2">
+        <v>0.30960470000000001</v>
+      </c>
+      <c r="I2">
         <f>AVERAGE(E2:E34)</f>
         <v>0.16480556060606061</v>
       </c>
-      <c r="I2">
+      <c r="J2">
         <f>AVERAGE(F2:F34)</f>
         <v>0.32585080454545451</v>
       </c>
-      <c r="J2">
+      <c r="K2">
         <f>AVERAGE(G2:G34)</f>
         <v>0.34796175161290316</v>
       </c>
-    </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="L2">
+        <f>AVERAGE(H2:H34)</f>
+        <v>0.25356534166666667</v>
+      </c>
+    </row>
+    <row r="3" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A3">
         <v>10.44</v>
       </c>
@@ -2630,19 +2926,26 @@
         <v>0.49857610000000002</v>
       </c>
       <c r="H3">
-        <f>H2</f>
+        <v>0.24119489999999999</v>
+      </c>
+      <c r="I3">
+        <f>I2</f>
         <v>0.16480556060606061</v>
       </c>
-      <c r="I3">
-        <f t="shared" ref="I3:I34" si="0">I2</f>
+      <c r="J3">
+        <f t="shared" ref="J3:J34" si="0">J2</f>
         <v>0.32585080454545451</v>
       </c>
-      <c r="J3">
-        <f t="shared" ref="J3:J34" si="1">J2</f>
+      <c r="K3">
+        <f t="shared" ref="K3:L34" si="1">K2</f>
         <v>0.34796175161290316</v>
       </c>
-    </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="L3">
+        <f t="shared" si="1"/>
+        <v>0.25356534166666667</v>
+      </c>
+    </row>
+    <row r="4" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A4">
         <v>13.72</v>
       </c>
@@ -2662,19 +2965,26 @@
         <v>0.50467379999999995</v>
       </c>
       <c r="H4">
-        <f t="shared" ref="H4:H34" si="2">H3</f>
+        <v>0.42393150000000002</v>
+      </c>
+      <c r="I4">
+        <f t="shared" ref="I4:I34" si="2">I3</f>
         <v>0.16480556060606061</v>
       </c>
-      <c r="I4">
+      <c r="J4">
         <f t="shared" si="0"/>
         <v>0.32585080454545451</v>
       </c>
-      <c r="J4">
+      <c r="K4">
         <f t="shared" si="1"/>
         <v>0.34796175161290316</v>
       </c>
-    </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="L4">
+        <f t="shared" si="1"/>
+        <v>0.25356534166666667</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A5">
         <v>4.7</v>
       </c>
@@ -2694,19 +3004,26 @@
         <v>0.44822899999999999</v>
       </c>
       <c r="H5">
+        <v>0.17542440000000001</v>
+      </c>
+      <c r="I5">
         <f t="shared" si="2"/>
         <v>0.16480556060606061</v>
       </c>
-      <c r="I5">
+      <c r="J5">
         <f t="shared" si="0"/>
         <v>0.32585080454545451</v>
       </c>
-      <c r="J5">
+      <c r="K5">
         <f t="shared" si="1"/>
         <v>0.34796175161290316</v>
       </c>
-    </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="L5">
+        <f t="shared" si="1"/>
+        <v>0.25356534166666667</v>
+      </c>
+    </row>
+    <row r="6" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A6">
         <v>2.96</v>
       </c>
@@ -2726,19 +3043,26 @@
         <v>0.33865119999999999</v>
       </c>
       <c r="H6">
+        <v>0.19900319999999999</v>
+      </c>
+      <c r="I6">
         <f t="shared" si="2"/>
         <v>0.16480556060606061</v>
       </c>
-      <c r="I6">
+      <c r="J6">
         <f t="shared" si="0"/>
         <v>0.32585080454545451</v>
       </c>
-      <c r="J6">
+      <c r="K6">
         <f t="shared" si="1"/>
         <v>0.34796175161290316</v>
       </c>
-    </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="L6">
+        <f t="shared" si="1"/>
+        <v>0.25356534166666667</v>
+      </c>
+    </row>
+    <row r="7" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A7">
         <v>6.24</v>
       </c>
@@ -2758,19 +3082,26 @@
         <v>0.43868370000000001</v>
       </c>
       <c r="H7">
+        <v>0.30479679999999998</v>
+      </c>
+      <c r="I7">
         <f t="shared" si="2"/>
         <v>0.16480556060606061</v>
       </c>
-      <c r="I7">
+      <c r="J7">
         <f t="shared" si="0"/>
         <v>0.32585080454545451</v>
       </c>
-      <c r="J7">
+      <c r="K7">
         <f t="shared" si="1"/>
         <v>0.34796175161290316</v>
       </c>
-    </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="L7">
+        <f t="shared" si="1"/>
+        <v>0.25356534166666667</v>
+      </c>
+    </row>
+    <row r="8" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A8">
         <v>9.52</v>
       </c>
@@ -2790,19 +3121,26 @@
         <v>0.53622959999999997</v>
       </c>
       <c r="H8">
+        <v>0.23587359999999999</v>
+      </c>
+      <c r="I8">
         <f t="shared" si="2"/>
         <v>0.16480556060606061</v>
       </c>
-      <c r="I8">
+      <c r="J8">
         <f t="shared" si="0"/>
         <v>0.32585080454545451</v>
       </c>
-      <c r="J8">
+      <c r="K8">
         <f t="shared" si="1"/>
         <v>0.34796175161290316</v>
       </c>
-    </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="L8">
+        <f t="shared" si="1"/>
+        <v>0.25356534166666667</v>
+      </c>
+    </row>
+    <row r="9" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A9">
         <v>3.04</v>
       </c>
@@ -2822,19 +3160,26 @@
         <v>0.2558318</v>
       </c>
       <c r="H9">
+        <v>0.19466820000000001</v>
+      </c>
+      <c r="I9">
         <f t="shared" si="2"/>
         <v>0.16480556060606061</v>
       </c>
-      <c r="I9">
+      <c r="J9">
         <f t="shared" si="0"/>
         <v>0.32585080454545451</v>
       </c>
-      <c r="J9">
+      <c r="K9">
         <f t="shared" si="1"/>
         <v>0.34796175161290316</v>
       </c>
-    </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="L9">
+        <f t="shared" si="1"/>
+        <v>0.25356534166666667</v>
+      </c>
+    </row>
+    <row r="10" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A10">
         <v>8.02</v>
       </c>
@@ -2854,19 +3199,26 @@
         <v>0.37833879999999998</v>
       </c>
       <c r="H10">
+        <v>0.31722230000000001</v>
+      </c>
+      <c r="I10">
         <f t="shared" si="2"/>
         <v>0.16480556060606061</v>
       </c>
-      <c r="I10">
+      <c r="J10">
         <f t="shared" si="0"/>
         <v>0.32585080454545451</v>
       </c>
-      <c r="J10">
+      <c r="K10">
         <f t="shared" si="1"/>
         <v>0.34796175161290316</v>
       </c>
-    </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="L10">
+        <f t="shared" si="1"/>
+        <v>0.25356534166666667</v>
+      </c>
+    </row>
+    <row r="11" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A11">
         <v>11.32</v>
       </c>
@@ -2886,19 +3238,26 @@
         <v>0.30457580000000001</v>
       </c>
       <c r="H11">
+        <v>0.22456699999999999</v>
+      </c>
+      <c r="I11">
         <f t="shared" si="2"/>
         <v>0.16480556060606061</v>
       </c>
-      <c r="I11">
+      <c r="J11">
         <f t="shared" si="0"/>
         <v>0.32585080454545451</v>
       </c>
-      <c r="J11">
+      <c r="K11">
         <f t="shared" si="1"/>
         <v>0.34796175161290316</v>
       </c>
-    </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="L11">
+        <f t="shared" si="1"/>
+        <v>0.25356534166666667</v>
+      </c>
+    </row>
+    <row r="12" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A12">
         <v>8.3000000000000007</v>
       </c>
@@ -2918,19 +3277,26 @@
         <v>0.18114450000000001</v>
       </c>
       <c r="H12">
+        <v>0.13658439999999999</v>
+      </c>
+      <c r="I12">
         <f t="shared" si="2"/>
         <v>0.16480556060606061</v>
       </c>
-      <c r="I12">
+      <c r="J12">
         <f t="shared" si="0"/>
         <v>0.32585080454545451</v>
       </c>
-      <c r="J12">
+      <c r="K12">
         <f t="shared" si="1"/>
         <v>0.34796175161290316</v>
       </c>
-    </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="L12">
+        <f t="shared" si="1"/>
+        <v>0.25356534166666667</v>
+      </c>
+    </row>
+    <row r="13" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A13">
         <v>11.8</v>
       </c>
@@ -2950,19 +3316,26 @@
         <v>0.21483749999999999</v>
       </c>
       <c r="H13">
+        <v>0.210925</v>
+      </c>
+      <c r="I13">
         <f t="shared" si="2"/>
         <v>0.16480556060606061</v>
       </c>
-      <c r="I13">
+      <c r="J13">
         <f t="shared" si="0"/>
         <v>0.32585080454545451</v>
       </c>
-      <c r="J13">
+      <c r="K13">
         <f t="shared" si="1"/>
         <v>0.34796175161290316</v>
       </c>
-    </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="L13">
+        <f t="shared" si="1"/>
+        <v>0.25356534166666667</v>
+      </c>
+    </row>
+    <row r="14" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A14">
         <v>14.94</v>
       </c>
@@ -2982,19 +3355,26 @@
         <v>0.3590544</v>
       </c>
       <c r="H14">
+        <v>0.22223200000000001</v>
+      </c>
+      <c r="I14">
         <f t="shared" si="2"/>
         <v>0.16480556060606061</v>
       </c>
-      <c r="I14">
+      <c r="J14">
         <f t="shared" si="0"/>
         <v>0.32585080454545451</v>
       </c>
-      <c r="J14">
+      <c r="K14">
         <f t="shared" si="1"/>
         <v>0.34796175161290316</v>
       </c>
-    </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="L14">
+        <f t="shared" si="1"/>
+        <v>0.25356534166666667</v>
+      </c>
+    </row>
+    <row r="15" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A15">
         <v>18.399999999999999</v>
       </c>
@@ -3014,19 +3394,26 @@
         <v>0.31738810000000001</v>
       </c>
       <c r="H15">
+        <v>0.23358699999999999</v>
+      </c>
+      <c r="I15">
         <f t="shared" si="2"/>
         <v>0.16480556060606061</v>
       </c>
-      <c r="I15">
+      <c r="J15">
         <f t="shared" si="0"/>
         <v>0.32585080454545451</v>
       </c>
-      <c r="J15">
+      <c r="K15">
         <f t="shared" si="1"/>
         <v>0.34796175161290316</v>
       </c>
-    </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="L15">
+        <f t="shared" si="1"/>
+        <v>0.25356534166666667</v>
+      </c>
+    </row>
+    <row r="16" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A16">
         <v>21.82</v>
       </c>
@@ -3046,19 +3433,26 @@
         <v>0.22177060000000001</v>
       </c>
       <c r="H16">
+        <v>0.29023840000000001</v>
+      </c>
+      <c r="I16">
         <f t="shared" si="2"/>
         <v>0.16480556060606061</v>
       </c>
-      <c r="I16">
+      <c r="J16">
         <f t="shared" si="0"/>
         <v>0.32585080454545451</v>
       </c>
-      <c r="J16">
+      <c r="K16">
         <f t="shared" si="1"/>
         <v>0.34796175161290316</v>
       </c>
-    </row>
-    <row r="17" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="L16">
+        <f t="shared" si="1"/>
+        <v>0.25356534166666667</v>
+      </c>
+    </row>
+    <row r="17" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A17">
         <v>25.6</v>
       </c>
@@ -3078,19 +3472,26 @@
         <v>0.1848128</v>
       </c>
       <c r="H17">
+        <v>0.29136600000000001</v>
+      </c>
+      <c r="I17">
         <f t="shared" si="2"/>
         <v>0.16480556060606061</v>
       </c>
-      <c r="I17">
+      <c r="J17">
         <f t="shared" si="0"/>
         <v>0.32585080454545451</v>
       </c>
-      <c r="J17">
+      <c r="K17">
         <f t="shared" si="1"/>
         <v>0.34796175161290316</v>
       </c>
-    </row>
-    <row r="18" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="L17">
+        <f t="shared" si="1"/>
+        <v>0.25356534166666667</v>
+      </c>
+    </row>
+    <row r="18" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A18">
         <v>29.48</v>
       </c>
@@ -3110,19 +3511,26 @@
         <v>0.27817530000000001</v>
       </c>
       <c r="H18">
+        <v>0.1194267</v>
+      </c>
+      <c r="I18">
         <f t="shared" si="2"/>
         <v>0.16480556060606061</v>
       </c>
-      <c r="I18">
+      <c r="J18">
         <f t="shared" si="0"/>
         <v>0.32585080454545451</v>
       </c>
-      <c r="J18">
+      <c r="K18">
         <f t="shared" si="1"/>
         <v>0.34796175161290316</v>
       </c>
-    </row>
-    <row r="19" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="L18">
+        <f t="shared" si="1"/>
+        <v>0.25356534166666667</v>
+      </c>
+    </row>
+    <row r="19" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A19">
         <v>34.28</v>
       </c>
@@ -3142,19 +3550,26 @@
         <v>0.34361900000000001</v>
       </c>
       <c r="H19">
+        <v>0.26140530000000001</v>
+      </c>
+      <c r="I19">
         <f t="shared" si="2"/>
         <v>0.16480556060606061</v>
       </c>
-      <c r="I19">
+      <c r="J19">
         <f t="shared" si="0"/>
         <v>0.32585080454545451</v>
       </c>
-      <c r="J19">
+      <c r="K19">
         <f t="shared" si="1"/>
         <v>0.34796175161290316</v>
       </c>
-    </row>
-    <row r="20" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="L19">
+        <f t="shared" si="1"/>
+        <v>0.25356534166666667</v>
+      </c>
+    </row>
+    <row r="20" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A20">
         <v>37.700000000000003</v>
       </c>
@@ -3174,19 +3589,26 @@
         <v>0.43726520000000002</v>
       </c>
       <c r="H20">
+        <v>0.20653779999999999</v>
+      </c>
+      <c r="I20">
         <f t="shared" si="2"/>
         <v>0.16480556060606061</v>
       </c>
-      <c r="I20">
+      <c r="J20">
         <f t="shared" si="0"/>
         <v>0.32585080454545451</v>
       </c>
-      <c r="J20">
+      <c r="K20">
         <f t="shared" si="1"/>
         <v>0.34796175161290316</v>
       </c>
-    </row>
-    <row r="21" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="L20">
+        <f t="shared" si="1"/>
+        <v>0.25356534166666667</v>
+      </c>
+    </row>
+    <row r="21" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A21">
         <v>41.2</v>
       </c>
@@ -3206,19 +3628,26 @@
         <v>0.28444550000000002</v>
       </c>
       <c r="H21">
+        <v>0.24643580000000001</v>
+      </c>
+      <c r="I21">
         <f t="shared" si="2"/>
         <v>0.16480556060606061</v>
       </c>
-      <c r="I21">
+      <c r="J21">
         <f t="shared" si="0"/>
         <v>0.32585080454545451</v>
       </c>
-      <c r="J21">
+      <c r="K21">
         <f t="shared" si="1"/>
         <v>0.34796175161290316</v>
       </c>
-    </row>
-    <row r="22" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="L21">
+        <f t="shared" si="1"/>
+        <v>0.25356534166666667</v>
+      </c>
+    </row>
+    <row r="22" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A22">
         <v>44.94</v>
       </c>
@@ -3238,19 +3667,26 @@
         <v>0.47699249999999999</v>
       </c>
       <c r="H22">
+        <v>0.35012680000000002</v>
+      </c>
+      <c r="I22">
         <f t="shared" si="2"/>
         <v>0.16480556060606061</v>
       </c>
-      <c r="I22">
+      <c r="J22">
         <f t="shared" si="0"/>
         <v>0.32585080454545451</v>
       </c>
-      <c r="J22">
+      <c r="K22">
         <f t="shared" si="1"/>
         <v>0.34796175161290316</v>
       </c>
-    </row>
-    <row r="23" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="L22">
+        <f t="shared" si="1"/>
+        <v>0.25356534166666667</v>
+      </c>
+    </row>
+    <row r="23" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A23">
         <v>55.52</v>
       </c>
@@ -3270,19 +3706,26 @@
         <v>0.4156436</v>
       </c>
       <c r="H23">
+        <v>0.24102000000000001</v>
+      </c>
+      <c r="I23">
         <f t="shared" si="2"/>
         <v>0.16480556060606061</v>
       </c>
-      <c r="I23">
+      <c r="J23">
         <f t="shared" si="0"/>
         <v>0.32585080454545451</v>
       </c>
-      <c r="J23">
+      <c r="K23">
         <f t="shared" si="1"/>
         <v>0.34796175161290316</v>
       </c>
-    </row>
-    <row r="24" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="L23">
+        <f t="shared" si="1"/>
+        <v>0.25356534166666667</v>
+      </c>
+    </row>
+    <row r="24" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A24">
         <v>58.88</v>
       </c>
@@ -3302,19 +3745,26 @@
         <v>0.25867970000000001</v>
       </c>
       <c r="H24">
+        <v>0.30813099999999999</v>
+      </c>
+      <c r="I24">
         <f t="shared" si="2"/>
         <v>0.16480556060606061</v>
       </c>
-      <c r="I24">
+      <c r="J24">
         <f t="shared" si="0"/>
         <v>0.32585080454545451</v>
       </c>
-      <c r="J24">
+      <c r="K24">
         <f t="shared" si="1"/>
         <v>0.34796175161290316</v>
       </c>
-    </row>
-    <row r="25" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="L24">
+        <f t="shared" si="1"/>
+        <v>0.25356534166666667</v>
+      </c>
+    </row>
+    <row r="25" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A25">
         <v>62.22</v>
       </c>
@@ -3334,19 +3784,26 @@
         <v>0.48689729999999998</v>
       </c>
       <c r="H25">
+        <v>0.3412654</v>
+      </c>
+      <c r="I25">
         <f t="shared" si="2"/>
         <v>0.16480556060606061</v>
       </c>
-      <c r="I25">
+      <c r="J25">
         <f t="shared" si="0"/>
         <v>0.32585080454545451</v>
       </c>
-      <c r="J25">
+      <c r="K25">
         <f t="shared" si="1"/>
         <v>0.34796175161290316</v>
       </c>
-    </row>
-    <row r="26" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="L25">
+        <f t="shared" si="1"/>
+        <v>0.25356534166666667</v>
+      </c>
+    </row>
+    <row r="26" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A26">
         <v>65.900000000000006</v>
       </c>
@@ -3365,20 +3822,24 @@
       <c r="G26">
         <v>0.30819410000000003</v>
       </c>
-      <c r="H26">
+      <c r="I26">
         <f t="shared" si="2"/>
         <v>0.16480556060606061</v>
       </c>
-      <c r="I26">
+      <c r="J26">
         <f t="shared" si="0"/>
         <v>0.32585080454545451</v>
       </c>
-      <c r="J26">
+      <c r="K26">
         <f t="shared" si="1"/>
         <v>0.34796175161290316</v>
       </c>
-    </row>
-    <row r="27" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="L26">
+        <f t="shared" si="1"/>
+        <v>0.25356534166666667</v>
+      </c>
+    </row>
+    <row r="27" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A27">
         <v>69.2</v>
       </c>
@@ -3397,20 +3858,24 @@
       <c r="G27">
         <v>0.40028900000000001</v>
       </c>
-      <c r="H27">
+      <c r="I27">
         <f t="shared" si="2"/>
         <v>0.16480556060606061</v>
       </c>
-      <c r="I27">
+      <c r="J27">
         <f t="shared" si="0"/>
         <v>0.32585080454545451</v>
       </c>
-      <c r="J27">
+      <c r="K27">
         <f t="shared" si="1"/>
         <v>0.34796175161290316</v>
       </c>
-    </row>
-    <row r="28" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="L27">
+        <f t="shared" si="1"/>
+        <v>0.25356534166666667</v>
+      </c>
+    </row>
+    <row r="28" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A28">
         <v>73.02</v>
       </c>
@@ -3429,20 +3894,24 @@
       <c r="G28">
         <v>0.23544080000000001</v>
       </c>
-      <c r="H28">
+      <c r="I28">
         <f t="shared" si="2"/>
         <v>0.16480556060606061</v>
       </c>
-      <c r="I28">
+      <c r="J28">
         <f t="shared" si="0"/>
         <v>0.32585080454545451</v>
       </c>
-      <c r="J28">
+      <c r="K28">
         <f t="shared" si="1"/>
         <v>0.34796175161290316</v>
       </c>
-    </row>
-    <row r="29" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="L28">
+        <f t="shared" si="1"/>
+        <v>0.25356534166666667</v>
+      </c>
+    </row>
+    <row r="29" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A29">
         <v>76.459999999999994</v>
       </c>
@@ -3461,20 +3930,24 @@
       <c r="G29">
         <v>0.13908039999999999</v>
       </c>
-      <c r="H29">
+      <c r="I29">
         <f t="shared" si="2"/>
         <v>0.16480556060606061</v>
       </c>
-      <c r="I29">
+      <c r="J29">
         <f t="shared" si="0"/>
         <v>0.32585080454545451</v>
       </c>
-      <c r="J29">
+      <c r="K29">
         <f t="shared" si="1"/>
         <v>0.34796175161290316</v>
       </c>
-    </row>
-    <row r="30" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="L29">
+        <f t="shared" si="1"/>
+        <v>0.25356534166666667</v>
+      </c>
+    </row>
+    <row r="30" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A30">
         <v>80.400000000000006</v>
       </c>
@@ -3493,20 +3966,24 @@
       <c r="G30">
         <v>0.2969156</v>
       </c>
-      <c r="H30">
+      <c r="I30">
         <f t="shared" si="2"/>
         <v>0.16480556060606061</v>
       </c>
-      <c r="I30">
+      <c r="J30">
         <f t="shared" si="0"/>
         <v>0.32585080454545451</v>
       </c>
-      <c r="J30">
+      <c r="K30">
         <f t="shared" si="1"/>
         <v>0.34796175161290316</v>
       </c>
-    </row>
-    <row r="31" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="L30">
+        <f t="shared" si="1"/>
+        <v>0.25356534166666667</v>
+      </c>
+    </row>
+    <row r="31" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A31">
         <v>83.64</v>
       </c>
@@ -3525,20 +4002,24 @@
       <c r="G31">
         <v>0.3955361</v>
       </c>
-      <c r="H31">
+      <c r="I31">
         <f t="shared" si="2"/>
         <v>0.16480556060606061</v>
       </c>
-      <c r="I31">
+      <c r="J31">
         <f t="shared" si="0"/>
         <v>0.32585080454545451</v>
       </c>
-      <c r="J31">
+      <c r="K31">
         <f t="shared" si="1"/>
         <v>0.34796175161290316</v>
       </c>
-    </row>
-    <row r="32" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="L31">
+        <f t="shared" si="1"/>
+        <v>0.25356534166666667</v>
+      </c>
+    </row>
+    <row r="32" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A32">
         <v>86.78</v>
       </c>
@@ -3557,20 +4038,24 @@
       <c r="G32">
         <v>0.53749239999999998</v>
       </c>
-      <c r="H32">
+      <c r="I32">
         <f t="shared" si="2"/>
         <v>0.16480556060606061</v>
       </c>
-      <c r="I32">
+      <c r="J32">
         <f t="shared" si="0"/>
         <v>0.32585080454545451</v>
       </c>
-      <c r="J32">
+      <c r="K32">
         <f t="shared" si="1"/>
         <v>0.34796175161290316</v>
       </c>
-    </row>
-    <row r="33" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="L32">
+        <f t="shared" si="1"/>
+        <v>0.25356534166666667</v>
+      </c>
+    </row>
+    <row r="33" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A33">
         <v>93.72</v>
       </c>
@@ -3586,20 +4071,24 @@
       <c r="F33">
         <v>0.44256010000000001</v>
       </c>
-      <c r="H33">
+      <c r="I33">
         <f t="shared" si="2"/>
         <v>0.16480556060606061</v>
       </c>
-      <c r="I33">
+      <c r="J33">
         <f t="shared" si="0"/>
         <v>0.32585080454545451</v>
       </c>
-      <c r="J33">
+      <c r="K33">
         <f t="shared" si="1"/>
         <v>0.34796175161290316</v>
       </c>
-    </row>
-    <row r="34" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="L33">
+        <f t="shared" si="1"/>
+        <v>0.25356534166666667</v>
+      </c>
+    </row>
+    <row r="34" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A34">
         <v>97.16</v>
       </c>
@@ -3615,20 +4104,24 @@
       <c r="F34">
         <v>0.41542780000000001</v>
       </c>
-      <c r="H34">
+      <c r="I34">
         <f t="shared" si="2"/>
         <v>0.16480556060606061</v>
       </c>
-      <c r="I34">
+      <c r="J34">
         <f t="shared" si="0"/>
         <v>0.32585080454545451</v>
       </c>
-      <c r="J34">
+      <c r="K34">
         <f t="shared" si="1"/>
         <v>0.34796175161290316</v>
       </c>
-    </row>
-    <row r="35" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="L34">
+        <f t="shared" si="1"/>
+        <v>0.25356534166666667</v>
+      </c>
+    </row>
+    <row r="35" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A35">
         <v>100.5</v>
       </c>
@@ -3639,7 +4132,7 @@
         <v>0.39007459999999999</v>
       </c>
     </row>
-    <row r="36" spans="1:10" x14ac:dyDescent="0.4">
+    <row r="36" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A36">
         <v>104</v>
       </c>
@@ -3650,7 +4143,7 @@
         <v>0.23385510000000001</v>
       </c>
     </row>
-    <row r="37" spans="1:10" x14ac:dyDescent="0.4">
+    <row r="37" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A37">
         <v>107.54</v>
       </c>
@@ -3661,7 +4154,7 @@
         <v>0.33364640000000001</v>
       </c>
     </row>
-    <row r="38" spans="1:10" x14ac:dyDescent="0.4">
+    <row r="38" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A38">
         <v>110.8</v>
       </c>
@@ -3672,7 +4165,7 @@
         <v>0.2872054</v>
       </c>
     </row>
-    <row r="39" spans="1:10" x14ac:dyDescent="0.4">
+    <row r="39" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A39">
         <v>117.02</v>
       </c>
@@ -3683,7 +4176,7 @@
         <v>0.22775680000000001</v>
       </c>
     </row>
-    <row r="40" spans="1:10" x14ac:dyDescent="0.4">
+    <row r="40" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A40">
         <v>120.06</v>
       </c>
@@ -3694,7 +4187,7 @@
         <v>0.2206854</v>
       </c>
     </row>
-    <row r="41" spans="1:10" x14ac:dyDescent="0.4">
+    <row r="41" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A41">
         <v>123.24</v>
       </c>
@@ -3705,7 +4198,7 @@
         <v>0.26762180000000002</v>
       </c>
     </row>
-    <row r="42" spans="1:10" x14ac:dyDescent="0.4">
+    <row r="42" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A42">
         <v>129.08000000000001</v>
       </c>
@@ -3716,7 +4209,7 @@
         <v>0.32549339999999999</v>
       </c>
     </row>
-    <row r="43" spans="1:10" x14ac:dyDescent="0.4">
+    <row r="43" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A43">
         <v>132.54</v>
       </c>
@@ -3727,7 +4220,7 @@
         <v>0.44256010000000001</v>
       </c>
     </row>
-    <row r="44" spans="1:10" x14ac:dyDescent="0.4">
+    <row r="44" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A44">
         <v>136.34</v>
       </c>
@@ -3738,7 +4231,7 @@
         <v>0.41542780000000001</v>
       </c>
     </row>
-    <row r="45" spans="1:10" x14ac:dyDescent="0.4">
+    <row r="45" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A45">
         <v>2.52</v>
       </c>
@@ -3749,7 +4242,7 @@
         <v>0.19148670000000001</v>
       </c>
     </row>
-    <row r="46" spans="1:10" x14ac:dyDescent="0.4">
+    <row r="46" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A46">
         <v>5.86</v>
       </c>
@@ -3760,7 +4253,7 @@
         <v>0.17124519999999999</v>
       </c>
     </row>
-    <row r="47" spans="1:10" x14ac:dyDescent="0.4">
+    <row r="47" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A47">
         <v>9.0999990000000004</v>
       </c>
@@ -3771,7 +4264,7 @@
         <v>0.10429380000000001</v>
       </c>
     </row>
-    <row r="48" spans="1:10" x14ac:dyDescent="0.4">
+    <row r="48" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A48">
         <v>12.22</v>
       </c>
@@ -4330,6 +4823,270 @@
       </c>
       <c r="C98">
         <v>0.53749239999999998</v>
+      </c>
+    </row>
+    <row r="99" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A99">
+        <v>20.2</v>
+      </c>
+      <c r="B99" t="s">
+        <v>6</v>
+      </c>
+      <c r="C99">
+        <v>0.30960470000000001</v>
+      </c>
+    </row>
+    <row r="100" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A100">
+        <v>29.78</v>
+      </c>
+      <c r="B100" t="s">
+        <v>6</v>
+      </c>
+      <c r="C100">
+        <v>0.24119489999999999</v>
+      </c>
+    </row>
+    <row r="101" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A101">
+        <v>33.840000000000003</v>
+      </c>
+      <c r="B101" t="s">
+        <v>6</v>
+      </c>
+      <c r="C101">
+        <v>0.42393150000000002</v>
+      </c>
+    </row>
+    <row r="102" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A102">
+        <v>37.9</v>
+      </c>
+      <c r="B102" t="s">
+        <v>6</v>
+      </c>
+      <c r="C102">
+        <v>0.17542440000000001</v>
+      </c>
+    </row>
+    <row r="103" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A103">
+        <v>41.82</v>
+      </c>
+      <c r="B103" t="s">
+        <v>6</v>
+      </c>
+      <c r="C103">
+        <v>0.19900319999999999</v>
+      </c>
+    </row>
+    <row r="104" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A104">
+        <v>46.2</v>
+      </c>
+      <c r="B104" t="s">
+        <v>6</v>
+      </c>
+      <c r="C104">
+        <v>0.30479679999999998</v>
+      </c>
+    </row>
+    <row r="105" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A105">
+        <v>50.62</v>
+      </c>
+      <c r="B105" t="s">
+        <v>6</v>
+      </c>
+      <c r="C105">
+        <v>0.23587359999999999</v>
+      </c>
+    </row>
+    <row r="106" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A106">
+        <v>56.32</v>
+      </c>
+      <c r="B106" t="s">
+        <v>6</v>
+      </c>
+      <c r="C106">
+        <v>0.19466820000000001</v>
+      </c>
+    </row>
+    <row r="107" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A107">
+        <v>61.36</v>
+      </c>
+      <c r="B107" t="s">
+        <v>6</v>
+      </c>
+      <c r="C107">
+        <v>0.31722230000000001</v>
+      </c>
+    </row>
+    <row r="108" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A108">
+        <v>65.680000000000007</v>
+      </c>
+      <c r="B108" t="s">
+        <v>6</v>
+      </c>
+      <c r="C108">
+        <v>0.22456699999999999</v>
+      </c>
+    </row>
+    <row r="109" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A109">
+        <v>70.36</v>
+      </c>
+      <c r="B109" t="s">
+        <v>6</v>
+      </c>
+      <c r="C109">
+        <v>0.13658439999999999</v>
+      </c>
+    </row>
+    <row r="110" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A110">
+        <v>80.34</v>
+      </c>
+      <c r="B110" t="s">
+        <v>6</v>
+      </c>
+      <c r="C110">
+        <v>0.210925</v>
+      </c>
+    </row>
+    <row r="111" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A111">
+        <v>84.9</v>
+      </c>
+      <c r="B111" t="s">
+        <v>6</v>
+      </c>
+      <c r="C111">
+        <v>0.22223200000000001</v>
+      </c>
+    </row>
+    <row r="112" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A112">
+        <v>94.759990000000002</v>
+      </c>
+      <c r="B112" t="s">
+        <v>6</v>
+      </c>
+      <c r="C112">
+        <v>0.23358699999999999</v>
+      </c>
+    </row>
+    <row r="113" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A113">
+        <v>98.86</v>
+      </c>
+      <c r="B113" t="s">
+        <v>6</v>
+      </c>
+      <c r="C113">
+        <v>0.29023840000000001</v>
+      </c>
+    </row>
+    <row r="114" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A114">
+        <v>102.72</v>
+      </c>
+      <c r="B114" t="s">
+        <v>6</v>
+      </c>
+      <c r="C114">
+        <v>0.29136600000000001</v>
+      </c>
+    </row>
+    <row r="115" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A115">
+        <v>111.62</v>
+      </c>
+      <c r="B115" t="s">
+        <v>6</v>
+      </c>
+      <c r="C115">
+        <v>0.1194267</v>
+      </c>
+    </row>
+    <row r="116" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A116">
+        <v>115.96</v>
+      </c>
+      <c r="B116" t="s">
+        <v>6</v>
+      </c>
+      <c r="C116">
+        <v>0.26140530000000001</v>
+      </c>
+    </row>
+    <row r="117" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A117">
+        <v>119.96</v>
+      </c>
+      <c r="B117" t="s">
+        <v>6</v>
+      </c>
+      <c r="C117">
+        <v>0.20653779999999999</v>
+      </c>
+    </row>
+    <row r="118" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A118">
+        <v>124.64</v>
+      </c>
+      <c r="B118" t="s">
+        <v>6</v>
+      </c>
+      <c r="C118">
+        <v>0.24643580000000001</v>
+      </c>
+    </row>
+    <row r="119" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A119">
+        <v>128.56</v>
+      </c>
+      <c r="B119" t="s">
+        <v>6</v>
+      </c>
+      <c r="C119">
+        <v>0.35012680000000002</v>
+      </c>
+    </row>
+    <row r="120" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A120">
+        <v>133.32</v>
+      </c>
+      <c r="B120" t="s">
+        <v>6</v>
+      </c>
+      <c r="C120">
+        <v>0.24102000000000001</v>
+      </c>
+    </row>
+    <row r="121" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A121">
+        <v>137.72</v>
+      </c>
+      <c r="B121" t="s">
+        <v>6</v>
+      </c>
+      <c r="C121">
+        <v>0.30813099999999999</v>
+      </c>
+    </row>
+    <row r="122" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A122">
+        <v>141.88</v>
+      </c>
+      <c r="B122" t="s">
+        <v>6</v>
+      </c>
+      <c r="C122">
+        <v>0.3412654</v>
       </c>
     </row>
   </sheetData>
